--- a/reports/20260803-20260809/城市经理问题闭环填写表_20260803-20260809.xlsx
+++ b/reports/20260803-20260809/城市经理问题闭环填写表_20260803-20260809.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="1" r:id="Rb2d571a6ef1c49d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="2" r:id="R1f79126701634770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="3" r:id="R6bebfb4daac54cce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="4" r:id="R16f6d830e5394f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="5" r:id="Ra608c86c31134c79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="1" r:id="R0c0eca1f11174647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="2" r:id="R90f03bc703124eb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="3" r:id="R78c47331fc024a97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="4" r:id="Rd073a839f1cf4fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="5" r:id="Rb555cc93d5b64ebc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -430,7 +430,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>对象</x:v>
+        <x:v>门店名称</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
         <x:v>上周异常/本周结果</x:v>
@@ -887,7 +887,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>对象</x:v>
+        <x:v>门店名称</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
         <x:v>上周异常/本周结果</x:v>
@@ -1044,7 +1044,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>对象</x:v>
+        <x:v>门店名称</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
         <x:v>上周异常/本周结果</x:v>
@@ -1221,7 +1221,7 @@
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
       <x:c r="A1" s="7" t="str">
-        <x:v>对象</x:v>
+        <x:v>门店名称</x:v>
       </x:c>
       <x:c r="B1" s="8" t="str">
         <x:v>上周异常/本周结果</x:v>
